--- a/gu_in/Item.edf/39_UnitLower/UnitLower.xlsx
+++ b/gu_in/Item.edf/39_UnitLower/UnitLower.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E10ACB-E694-48A4-89F5-FECD37900690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED240DE4-D37C-4B89-8428-BBC7CBA7937E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitLower" sheetId="1" r:id="rId1"/>
@@ -820,7 +820,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -829,8 +829,15 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -845,6 +852,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="42"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -878,17 +890,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -905,9 +920,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -945,9 +960,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -980,9 +995,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1015,9 +1047,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1192,60 +1241,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BB82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="34" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="34" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="9" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="40" max="41" width="7" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="9" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="9" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="9" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="9" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1409,7 +1458,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1571,7 +1620,7 @@
       </c>
       <c r="BB2" s="2"/>
     </row>
-    <row r="3" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>57</v>
       </c>
@@ -1734,7 +1783,7 @@
       </c>
       <c r="BB3" s="2"/>
     </row>
-    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>60</v>
       </c>
@@ -1897,7 +1946,7 @@
       </c>
       <c r="BB4" s="2"/>
     </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -2060,7 +2109,7 @@
       </c>
       <c r="BB5" s="2"/>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -2223,7 +2272,7 @@
       </c>
       <c r="BB6" s="2"/>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>63</v>
       </c>
@@ -2386,7 +2435,7 @@
       </c>
       <c r="BB7" s="2"/>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>64</v>
       </c>
@@ -2549,7 +2598,7 @@
       </c>
       <c r="BB8" s="2"/>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>65</v>
       </c>
@@ -2712,7 +2761,7 @@
       </c>
       <c r="BB9" s="2"/>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -2875,7 +2924,7 @@
       </c>
       <c r="BB10" s="2"/>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>68</v>
       </c>
@@ -3038,7 +3087,7 @@
       </c>
       <c r="BB11" s="2"/>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>70</v>
       </c>
@@ -3201,7 +3250,7 @@
       </c>
       <c r="BB12" s="2"/>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>72</v>
       </c>
@@ -3364,7 +3413,7 @@
       </c>
       <c r="BB13" s="2"/>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>74</v>
       </c>
@@ -3527,7 +3576,7 @@
       </c>
       <c r="BB14" s="2"/>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>75</v>
       </c>
@@ -3561,8 +3610,8 @@
       <c r="K15" s="2">
         <v>0</v>
       </c>
-      <c r="L15" s="3">
-        <v>49</v>
+      <c r="L15" s="5">
+        <v>51</v>
       </c>
       <c r="M15" s="3">
         <v>-1</v>
@@ -3690,7 +3739,7 @@
       </c>
       <c r="BB15" s="2"/>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>77</v>
       </c>
@@ -3724,8 +3773,8 @@
       <c r="K16" s="2">
         <v>0</v>
       </c>
-      <c r="L16" s="3">
-        <v>49</v>
+      <c r="L16" s="5">
+        <v>51</v>
       </c>
       <c r="M16" s="3">
         <v>-1</v>
@@ -3853,7 +3902,7 @@
       </c>
       <c r="BB16" s="2"/>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>78</v>
       </c>
@@ -3887,8 +3936,8 @@
       <c r="K17" s="2">
         <v>0</v>
       </c>
-      <c r="L17" s="3">
-        <v>49</v>
+      <c r="L17" s="5">
+        <v>51</v>
       </c>
       <c r="M17" s="3">
         <v>-1</v>
@@ -4016,7 +4065,7 @@
       </c>
       <c r="BB17" s="2"/>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>79</v>
       </c>
@@ -4179,7 +4228,7 @@
       </c>
       <c r="BB18" s="2"/>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>81</v>
       </c>
@@ -4342,7 +4391,7 @@
       </c>
       <c r="BB19" s="2"/>
     </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>82</v>
       </c>
@@ -4505,7 +4554,7 @@
       </c>
       <c r="BB20" s="2"/>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>83</v>
       </c>
@@ -4668,7 +4717,7 @@
       </c>
       <c r="BB21" s="2"/>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>85</v>
       </c>
@@ -4831,7 +4880,7 @@
       </c>
       <c r="BB22" s="2"/>
     </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>86</v>
       </c>
@@ -4994,7 +5043,7 @@
       </c>
       <c r="BB23" s="2"/>
     </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>89</v>
       </c>
@@ -5157,7 +5206,7 @@
       </c>
       <c r="BB24" s="2"/>
     </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>90</v>
       </c>
@@ -5320,7 +5369,7 @@
       </c>
       <c r="BB25" s="2"/>
     </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>91</v>
       </c>
@@ -5483,7 +5532,7 @@
       </c>
       <c r="BB26" s="2"/>
     </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>92</v>
       </c>
@@ -5646,7 +5695,7 @@
       </c>
       <c r="BB27" s="2"/>
     </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>93</v>
       </c>
@@ -5809,7 +5858,7 @@
       </c>
       <c r="BB28" s="2"/>
     </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>94</v>
       </c>
@@ -5972,7 +6021,7 @@
       </c>
       <c r="BB29" s="2"/>
     </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>95</v>
       </c>
@@ -6135,7 +6184,7 @@
       </c>
       <c r="BB30" s="2"/>
     </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>97</v>
       </c>
@@ -6298,7 +6347,7 @@
       </c>
       <c r="BB31" s="2"/>
     </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>99</v>
       </c>
@@ -6461,7 +6510,7 @@
       </c>
       <c r="BB32" s="2"/>
     </row>
-    <row r="33" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>101</v>
       </c>
@@ -6624,7 +6673,7 @@
       </c>
       <c r="BB33" s="2"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>103</v>
       </c>
@@ -6787,7 +6836,7 @@
       </c>
       <c r="BB34" s="2"/>
     </row>
-    <row r="35" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>104</v>
       </c>
@@ -6821,8 +6870,8 @@
       <c r="K35" s="2">
         <v>0</v>
       </c>
-      <c r="L35" s="3">
-        <v>49</v>
+      <c r="L35" s="5">
+        <v>51</v>
       </c>
       <c r="M35" s="3">
         <v>-1</v>
@@ -6950,7 +6999,7 @@
       </c>
       <c r="BB35" s="2"/>
     </row>
-    <row r="36" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>106</v>
       </c>
@@ -6984,8 +7033,8 @@
       <c r="K36" s="2">
         <v>0</v>
       </c>
-      <c r="L36" s="3">
-        <v>49</v>
+      <c r="L36" s="5">
+        <v>51</v>
       </c>
       <c r="M36" s="3">
         <v>-1</v>
@@ -7113,7 +7162,7 @@
       </c>
       <c r="BB36" s="2"/>
     </row>
-    <row r="37" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>107</v>
       </c>
@@ -7147,8 +7196,8 @@
       <c r="K37" s="2">
         <v>0</v>
       </c>
-      <c r="L37" s="3">
-        <v>49</v>
+      <c r="L37" s="5">
+        <v>51</v>
       </c>
       <c r="M37" s="3">
         <v>-1</v>
@@ -7276,7 +7325,7 @@
       </c>
       <c r="BB37" s="2"/>
     </row>
-    <row r="38" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>108</v>
       </c>
@@ -7439,7 +7488,7 @@
       </c>
       <c r="BB38" s="2"/>
     </row>
-    <row r="39" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>110</v>
       </c>
@@ -7602,7 +7651,7 @@
       </c>
       <c r="BB39" s="2"/>
     </row>
-    <row r="40" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>111</v>
       </c>
@@ -7765,7 +7814,7 @@
       </c>
       <c r="BB40" s="2"/>
     </row>
-    <row r="41" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>112</v>
       </c>
@@ -7928,7 +7977,7 @@
       </c>
       <c r="BB41" s="2"/>
     </row>
-    <row r="42" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>114</v>
       </c>
@@ -8091,7 +8140,7 @@
       </c>
       <c r="BB42" s="2"/>
     </row>
-    <row r="43" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>115</v>
       </c>
@@ -8254,7 +8303,7 @@
       </c>
       <c r="BB43" s="2"/>
     </row>
-    <row r="44" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>118</v>
       </c>
@@ -8417,7 +8466,7 @@
       </c>
       <c r="BB44" s="2"/>
     </row>
-    <row r="45" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>120</v>
       </c>
@@ -8580,7 +8629,7 @@
       </c>
       <c r="BB45" s="2"/>
     </row>
-    <row r="46" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>122</v>
       </c>
@@ -8743,7 +8792,7 @@
       </c>
       <c r="BB46" s="2"/>
     </row>
-    <row r="47" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>124</v>
       </c>
@@ -8906,7 +8955,7 @@
       </c>
       <c r="BB47" s="2"/>
     </row>
-    <row r="48" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>126</v>
       </c>
@@ -9069,7 +9118,7 @@
       </c>
       <c r="BB48" s="2"/>
     </row>
-    <row r="49" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>128</v>
       </c>
@@ -9232,7 +9281,7 @@
       </c>
       <c r="BB49" s="2"/>
     </row>
-    <row r="50" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>130</v>
       </c>
@@ -9395,7 +9444,7 @@
       </c>
       <c r="BB50" s="2"/>
     </row>
-    <row r="51" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>132</v>
       </c>
@@ -9558,7 +9607,7 @@
       </c>
       <c r="BB51" s="2"/>
     </row>
-    <row r="52" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>134</v>
       </c>
@@ -9721,7 +9770,7 @@
       </c>
       <c r="BB52" s="2"/>
     </row>
-    <row r="53" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>136</v>
       </c>
@@ -9884,7 +9933,7 @@
       </c>
       <c r="BB53" s="2"/>
     </row>
-    <row r="54" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>138</v>
       </c>
@@ -10047,7 +10096,7 @@
       </c>
       <c r="BB54" s="2"/>
     </row>
-    <row r="55" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>140</v>
       </c>
@@ -10210,7 +10259,7 @@
       </c>
       <c r="BB55" s="2"/>
     </row>
-    <row r="56" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>142</v>
       </c>
@@ -10373,7 +10422,7 @@
       </c>
       <c r="BB56" s="2"/>
     </row>
-    <row r="57" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>144</v>
       </c>
@@ -10536,7 +10585,7 @@
       </c>
       <c r="BB57" s="2"/>
     </row>
-    <row r="58" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>146</v>
       </c>
@@ -10699,7 +10748,7 @@
       </c>
       <c r="BB58" s="2"/>
     </row>
-    <row r="59" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>148</v>
       </c>
@@ -10862,7 +10911,7 @@
       </c>
       <c r="BB59" s="2"/>
     </row>
-    <row r="60" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>150</v>
       </c>
@@ -11025,7 +11074,7 @@
       </c>
       <c r="BB60" s="2"/>
     </row>
-    <row r="61" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>152</v>
       </c>
@@ -11188,7 +11237,7 @@
       </c>
       <c r="BB61" s="2"/>
     </row>
-    <row r="62" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>154</v>
       </c>
@@ -11351,7 +11400,7 @@
       </c>
       <c r="BB62" s="2"/>
     </row>
-    <row r="63" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>156</v>
       </c>
@@ -11514,7 +11563,7 @@
       </c>
       <c r="BB63" s="2"/>
     </row>
-    <row r="64" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>159</v>
       </c>
@@ -11677,7 +11726,7 @@
       </c>
       <c r="BB64" s="2"/>
     </row>
-    <row r="65" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>161</v>
       </c>
@@ -11840,7 +11889,7 @@
       </c>
       <c r="BB65" s="2"/>
     </row>
-    <row r="66" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>163</v>
       </c>
@@ -12003,7 +12052,7 @@
       </c>
       <c r="BB66" s="2"/>
     </row>
-    <row r="67" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>165</v>
       </c>
@@ -12166,7 +12215,7 @@
       </c>
       <c r="BB67" s="2"/>
     </row>
-    <row r="68" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>167</v>
       </c>
@@ -12329,7 +12378,7 @@
       </c>
       <c r="BB68" s="2"/>
     </row>
-    <row r="69" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>169</v>
       </c>
@@ -12492,7 +12541,7 @@
       </c>
       <c r="BB69" s="2"/>
     </row>
-    <row r="70" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>171</v>
       </c>
@@ -12655,7 +12704,7 @@
       </c>
       <c r="BB70" s="2"/>
     </row>
-    <row r="71" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>173</v>
       </c>
@@ -12818,7 +12867,7 @@
       </c>
       <c r="BB71" s="2"/>
     </row>
-    <row r="72" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>175</v>
       </c>
@@ -12981,7 +13030,7 @@
       </c>
       <c r="BB72" s="2"/>
     </row>
-    <row r="73" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>177</v>
       </c>
@@ -13144,7 +13193,7 @@
       </c>
       <c r="BB73" s="2"/>
     </row>
-    <row r="74" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>179</v>
       </c>
@@ -13307,7 +13356,7 @@
       </c>
       <c r="BB74" s="2"/>
     </row>
-    <row r="75" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>181</v>
       </c>
@@ -13470,7 +13519,7 @@
       </c>
       <c r="BB75" s="2"/>
     </row>
-    <row r="76" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>183</v>
       </c>
@@ -13633,7 +13682,7 @@
       </c>
       <c r="BB76" s="2"/>
     </row>
-    <row r="77" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>185</v>
       </c>
@@ -13796,7 +13845,7 @@
       </c>
       <c r="BB77" s="2"/>
     </row>
-    <row r="78" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>187</v>
       </c>
@@ -13959,7 +14008,7 @@
       </c>
       <c r="BB78" s="2"/>
     </row>
-    <row r="79" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>189</v>
       </c>
@@ -14122,7 +14171,7 @@
       </c>
       <c r="BB79" s="2"/>
     </row>
-    <row r="80" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>191</v>
       </c>
@@ -14285,7 +14334,7 @@
       </c>
       <c r="BB80" s="2"/>
     </row>
-    <row r="81" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>193</v>
       </c>
@@ -14448,7 +14497,7 @@
       </c>
       <c r="BB81" s="2"/>
     </row>
-    <row r="82" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>195</v>
       </c>
@@ -14620,53 +14669,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AZ82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="6" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="44" max="45" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="46" max="47" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="44" max="45" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="4.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>197</v>
       </c>
@@ -14824,7 +14873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>UnitLower!A2</f>
         <v>Code</v>
@@ -15004,7 +15053,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>UnitLower!A3</f>
         <v>unlo001</v>
@@ -15184,7 +15233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>UnitLower!A4</f>
         <v>unlo002</v>
@@ -15364,7 +15413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>UnitLower!A5</f>
         <v>unlo003</v>
@@ -15544,7 +15593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>UnitLower!A6</f>
         <v>unlo004</v>
@@ -15724,7 +15773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>UnitLower!A7</f>
         <v>unlo005</v>
@@ -15904,7 +15953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>UnitLower!A8</f>
         <v>unlo006</v>
@@ -16084,7 +16133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>UnitLower!A9</f>
         <v>unlo007</v>
@@ -16264,7 +16313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>UnitLower!A10</f>
         <v>unlo008</v>
@@ -16444,7 +16493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>UnitLower!A11</f>
         <v>unlo009</v>
@@ -16624,7 +16673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
         <f>UnitLower!A12</f>
         <v>unlo010</v>
@@ -16804,7 +16853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
         <f>UnitLower!A13</f>
         <v>unlo011</v>
@@ -16984,7 +17033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
         <f>UnitLower!A14</f>
         <v>unlo012</v>
@@ -17164,7 +17213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
         <f>UnitLower!A15</f>
         <v>unlo013</v>
@@ -17304,7 +17353,7 @@
       </c>
       <c r="AO15">
         <f>UnitLower!L15</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AP15">
         <f>UnitLower!N15</f>
@@ -17344,7 +17393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
         <f>UnitLower!A16</f>
         <v>unlo014</v>
@@ -17484,7 +17533,7 @@
       </c>
       <c r="AO16">
         <f>UnitLower!L16</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AP16">
         <f>UnitLower!N16</f>
@@ -17524,7 +17573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>UnitLower!A17</f>
         <v>unlo015</v>
@@ -17664,7 +17713,7 @@
       </c>
       <c r="AO17">
         <f>UnitLower!L17</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AP17">
         <f>UnitLower!N17</f>
@@ -17704,7 +17753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>UnitLower!A18</f>
         <v>unlo016</v>
@@ -17884,7 +17933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>UnitLower!A19</f>
         <v>unlo017</v>
@@ -18064,7 +18113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>UnitLower!A20</f>
         <v>unlo018</v>
@@ -18244,7 +18293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>UnitLower!A21</f>
         <v>unlo019</v>
@@ -18424,7 +18473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>UnitLower!A22</f>
         <v>unlo020</v>
@@ -18604,7 +18653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>UnitLower!A23</f>
         <v>unlo021</v>
@@ -18784,7 +18833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>UnitLower!A24</f>
         <v>unlo022</v>
@@ -18964,7 +19013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>UnitLower!A25</f>
         <v>unlo023</v>
@@ -19144,7 +19193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>UnitLower!A26</f>
         <v>unlo024</v>
@@ -19324,7 +19373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>UnitLower!A27</f>
         <v>unlo025</v>
@@ -19504,7 +19553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>UnitLower!A28</f>
         <v>unlo026</v>
@@ -19684,7 +19733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>UnitLower!A29</f>
         <v>unlo027</v>
@@ -19864,7 +19913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>UnitLower!A30</f>
         <v>unlo028</v>
@@ -20044,7 +20093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>UnitLower!A31</f>
         <v>unlo029</v>
@@ -20224,7 +20273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>UnitLower!A32</f>
         <v>unlo030</v>
@@ -20404,7 +20453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>UnitLower!A33</f>
         <v>unlo031</v>
@@ -20584,7 +20633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>UnitLower!A34</f>
         <v>unlo032</v>
@@ -20764,7 +20813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>UnitLower!A35</f>
         <v>unlo033</v>
@@ -20904,7 +20953,7 @@
       </c>
       <c r="AO35">
         <f>UnitLower!L35</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AP35">
         <f>UnitLower!N35</f>
@@ -20944,7 +20993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>UnitLower!A36</f>
         <v>unlo034</v>
@@ -21084,7 +21133,7 @@
       </c>
       <c r="AO36">
         <f>UnitLower!L36</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AP36">
         <f>UnitLower!N36</f>
@@ -21124,7 +21173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f>UnitLower!A37</f>
         <v>unlo035</v>
@@ -21264,7 +21313,7 @@
       </c>
       <c r="AO37">
         <f>UnitLower!L37</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AP37">
         <f>UnitLower!N37</f>
@@ -21304,7 +21353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f>UnitLower!A38</f>
         <v>unlo036</v>
@@ -21484,7 +21533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>UnitLower!A39</f>
         <v>unlo037</v>
@@ -21664,7 +21713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f>UnitLower!A40</f>
         <v>unlo038</v>
@@ -21844,7 +21893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f>UnitLower!A41</f>
         <v>unlo039</v>
@@ -22024,7 +22073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f>UnitLower!A42</f>
         <v>unlo040</v>
@@ -22204,7 +22253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f>UnitLower!A43</f>
         <v>unlo041</v>
@@ -22384,7 +22433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>UnitLower!A44</f>
         <v>unlo042</v>
@@ -22564,7 +22613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>UnitLower!A45</f>
         <v>unlo043</v>
@@ -22744,7 +22793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>UnitLower!A46</f>
         <v>unlo044</v>
@@ -22924,7 +22973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>UnitLower!A47</f>
         <v>unlo045</v>
@@ -23104,7 +23153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f>UnitLower!A48</f>
         <v>unlo046</v>
@@ -23284,7 +23333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f>UnitLower!A49</f>
         <v>unlo047</v>
@@ -23464,7 +23513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f>UnitLower!A50</f>
         <v>unlo048</v>
@@ -23644,7 +23693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f>UnitLower!A51</f>
         <v>unlo049</v>
@@ -23824,7 +23873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f>UnitLower!A52</f>
         <v>unlo050</v>
@@ -24004,7 +24053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f>UnitLower!A53</f>
         <v>unlo051</v>
@@ -24184,7 +24233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f>UnitLower!A54</f>
         <v>unlo052</v>
@@ -24364,7 +24413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f>UnitLower!A55</f>
         <v>unlo053</v>
@@ -24544,7 +24593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f>UnitLower!A56</f>
         <v>unlo054</v>
@@ -24724,7 +24773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f>UnitLower!A57</f>
         <v>unlo055</v>
@@ -24904,7 +24953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f>UnitLower!A58</f>
         <v>unlo056</v>
@@ -25084,7 +25133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A59" t="str">
         <f>UnitLower!A59</f>
         <v>unlo057</v>
@@ -25264,7 +25313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A60" t="str">
         <f>UnitLower!A60</f>
         <v>unlo058</v>
@@ -25444,7 +25493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A61" t="str">
         <f>UnitLower!A61</f>
         <v>unlo059</v>
@@ -25624,7 +25673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A62" t="str">
         <f>UnitLower!A62</f>
         <v>unlo060</v>
@@ -25804,7 +25853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A63" t="str">
         <f>UnitLower!A63</f>
         <v>unlo061</v>
@@ -25984,7 +26033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A64" t="str">
         <f>UnitLower!A64</f>
         <v>unlo062</v>
@@ -26164,7 +26213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A65" t="str">
         <f>UnitLower!A65</f>
         <v>unlo063</v>
@@ -26344,7 +26393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A66" t="str">
         <f>UnitLower!A66</f>
         <v>unlo064</v>
@@ -26524,7 +26573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A67" t="str">
         <f>UnitLower!A67</f>
         <v>unlo065</v>
@@ -26704,7 +26753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A68" t="str">
         <f>UnitLower!A68</f>
         <v>unlo066</v>
@@ -26884,7 +26933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A69" t="str">
         <f>UnitLower!A69</f>
         <v>unlo067</v>
@@ -27064,7 +27113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A70" t="str">
         <f>UnitLower!A70</f>
         <v>unlo068</v>
@@ -27244,7 +27293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A71" t="str">
         <f>UnitLower!A71</f>
         <v>unlo069</v>
@@ -27424,7 +27473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A72" t="str">
         <f>UnitLower!A72</f>
         <v>unlo070</v>
@@ -27604,7 +27653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A73" t="str">
         <f>UnitLower!A73</f>
         <v>unlo071</v>
@@ -27784,7 +27833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A74" t="str">
         <f>UnitLower!A74</f>
         <v>unlo072</v>
@@ -27964,7 +28013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A75" t="str">
         <f>UnitLower!A75</f>
         <v>unlo073</v>
@@ -28144,7 +28193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A76" t="str">
         <f>UnitLower!A76</f>
         <v>unlo074</v>
@@ -28324,7 +28373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A77" t="str">
         <f>UnitLower!A77</f>
         <v>unlo075</v>
@@ -28504,7 +28553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A78" t="str">
         <f>UnitLower!A78</f>
         <v>unlo076</v>
@@ -28684,7 +28733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A79" t="str">
         <f>UnitLower!A79</f>
         <v>unlo077</v>
@@ -28864,7 +28913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A80" t="str">
         <f>UnitLower!A80</f>
         <v>unlo078</v>
@@ -29044,7 +29093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A81" t="str">
         <f>UnitLower!A81</f>
         <v>unlo079</v>
@@ -29224,7 +29273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:51" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A82" t="str">
         <f>UnitLower!A82</f>
         <v>unlo080</v>
@@ -29413,9 +29462,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C82"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -29426,7 +29475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>202</v>
       </c>
@@ -29435,7 +29484,7 @@
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>0</v>
       </c>
@@ -29444,7 +29493,7 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -29453,7 +29502,7 @@
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -29462,7 +29511,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -29471,7 +29520,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -29480,7 +29529,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -29489,7 +29538,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -29498,7 +29547,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -29507,7 +29556,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -29516,7 +29565,7 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -29525,7 +29574,7 @@
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -29534,7 +29583,7 @@
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -29543,7 +29592,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -29552,7 +29601,7 @@
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -29561,7 +29610,7 @@
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -29570,7 +29619,7 @@
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
@@ -29579,7 +29628,7 @@
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -29588,7 +29637,7 @@
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -29597,7 +29646,7 @@
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -29606,7 +29655,7 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -29615,7 +29664,7 @@
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -29624,7 +29673,7 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -29633,7 +29682,7 @@
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>22</v>
       </c>
@@ -29642,7 +29691,7 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>23</v>
       </c>
@@ -29651,7 +29700,7 @@
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -29660,7 +29709,7 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>25</v>
       </c>
@@ -29669,7 +29718,7 @@
       </c>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>26</v>
       </c>
@@ -29678,7 +29727,7 @@
       </c>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>27</v>
       </c>
@@ -29687,7 +29736,7 @@
       </c>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>28</v>
       </c>
@@ -29696,7 +29745,7 @@
       </c>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>29</v>
       </c>
@@ -29705,7 +29754,7 @@
       </c>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -29714,7 +29763,7 @@
       </c>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>31</v>
       </c>
@@ -29723,7 +29772,7 @@
       </c>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>32</v>
       </c>
@@ -29732,7 +29781,7 @@
       </c>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>33</v>
       </c>
@@ -29741,7 +29790,7 @@
       </c>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>34</v>
       </c>
@@ -29750,7 +29799,7 @@
       </c>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>35</v>
       </c>
@@ -29759,7 +29808,7 @@
       </c>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -29768,7 +29817,7 @@
       </c>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>37</v>
       </c>
@@ -29777,7 +29826,7 @@
       </c>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>38</v>
       </c>
@@ -29786,7 +29835,7 @@
       </c>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>39</v>
       </c>
@@ -29795,7 +29844,7 @@
       </c>
       <c r="C42" s="2"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>40</v>
       </c>
@@ -29804,7 +29853,7 @@
       </c>
       <c r="C43" s="2"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>41</v>
       </c>
@@ -29813,7 +29862,7 @@
       </c>
       <c r="C44" s="2"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>42</v>
       </c>
@@ -29822,7 +29871,7 @@
       </c>
       <c r="C45" s="2"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>43</v>
       </c>
@@ -29831,7 +29880,7 @@
       </c>
       <c r="C46" s="2"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>44</v>
       </c>
@@ -29840,7 +29889,7 @@
       </c>
       <c r="C47" s="2"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>45</v>
       </c>
@@ -29849,7 +29898,7 @@
       </c>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>46</v>
       </c>
@@ -29858,7 +29907,7 @@
       </c>
       <c r="C49" s="2"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>47</v>
       </c>
@@ -29867,7 +29916,7 @@
       </c>
       <c r="C50" s="2"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>48</v>
       </c>
@@ -29876,7 +29925,7 @@
       </c>
       <c r="C51" s="2"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>49</v>
       </c>
@@ -29885,7 +29934,7 @@
       </c>
       <c r="C52" s="2"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>50</v>
       </c>
@@ -29894,7 +29943,7 @@
       </c>
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>51</v>
       </c>
@@ -29903,7 +29952,7 @@
       </c>
       <c r="C54" s="2"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>52</v>
       </c>
@@ -29912,7 +29961,7 @@
       </c>
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>53</v>
       </c>
@@ -29921,7 +29970,7 @@
       </c>
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>54</v>
       </c>
@@ -29930,7 +29979,7 @@
       </c>
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>55</v>
       </c>
@@ -29939,7 +29988,7 @@
       </c>
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>56</v>
       </c>
@@ -29948,7 +29997,7 @@
       </c>
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>57</v>
       </c>
@@ -29957,7 +30006,7 @@
       </c>
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>58</v>
       </c>
@@ -29966,7 +30015,7 @@
       </c>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>59</v>
       </c>
@@ -29975,7 +30024,7 @@
       </c>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>60</v>
       </c>
@@ -29984,7 +30033,7 @@
       </c>
       <c r="C63" s="2"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>61</v>
       </c>
@@ -29993,7 +30042,7 @@
       </c>
       <c r="C64" s="2"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>62</v>
       </c>
@@ -30002,7 +30051,7 @@
       </c>
       <c r="C65" s="2"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>63</v>
       </c>
@@ -30011,7 +30060,7 @@
       </c>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>64</v>
       </c>
@@ -30020,7 +30069,7 @@
       </c>
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>65</v>
       </c>
@@ -30029,7 +30078,7 @@
       </c>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>66</v>
       </c>
@@ -30038,7 +30087,7 @@
       </c>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>67</v>
       </c>
@@ -30047,7 +30096,7 @@
       </c>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>68</v>
       </c>
@@ -30056,7 +30105,7 @@
       </c>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>69</v>
       </c>
@@ -30065,7 +30114,7 @@
       </c>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>70</v>
       </c>
@@ -30074,7 +30123,7 @@
       </c>
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>71</v>
       </c>
@@ -30083,7 +30132,7 @@
       </c>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>72</v>
       </c>
@@ -30092,7 +30141,7 @@
       </c>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>73</v>
       </c>
@@ -30101,7 +30150,7 @@
       </c>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>74</v>
       </c>
@@ -30110,7 +30159,7 @@
       </c>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>75</v>
       </c>
@@ -30119,7 +30168,7 @@
       </c>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>76</v>
       </c>
@@ -30128,7 +30177,7 @@
       </c>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>77</v>
       </c>
@@ -30137,7 +30186,7 @@
       </c>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>78</v>
       </c>
@@ -30146,7 +30195,7 @@
       </c>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>79</v>
       </c>

--- a/gu_in/Item.edf/39_UnitLower/UnitLower.xlsx
+++ b/gu_in/Item.edf/39_UnitLower/UnitLower.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED240DE4-D37C-4B89-8428-BBC7CBA7937E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5285DFC6-E9C1-4533-A0EB-5EF904592C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -820,7 +820,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -836,8 +836,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -857,6 +864,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -890,20 +902,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -6673,168 +6690,168 @@
       </c>
       <c r="BB33" s="2"/>
     </row>
-    <row r="34" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:54" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" s="3">
+      <c r="B34" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="6">
         <v>5</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="E34" s="3">
-        <v>2</v>
-      </c>
-      <c r="F34" s="3" t="s">
+      <c r="E34" s="6">
+        <v>2</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="I34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J34" s="2">
-        <v>0</v>
-      </c>
-      <c r="K34" s="2">
-        <v>0</v>
-      </c>
-      <c r="L34" s="3">
+      <c r="G34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="H34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="I34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="J34" s="7">
+        <v>0</v>
+      </c>
+      <c r="K34" s="7">
+        <v>0</v>
+      </c>
+      <c r="L34" s="6">
         <v>45</v>
       </c>
-      <c r="M34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="N34" s="3">
-        <v>2</v>
-      </c>
-      <c r="O34" s="3">
+      <c r="M34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="N34" s="6">
+        <v>2</v>
+      </c>
+      <c r="O34" s="6">
         <v>78</v>
       </c>
-      <c r="P34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="Q34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="R34" s="2">
-        <v>1</v>
-      </c>
-      <c r="S34" s="2">
-        <v>0</v>
-      </c>
-      <c r="T34" s="2">
-        <v>0</v>
-      </c>
-      <c r="U34" s="2">
-        <v>0</v>
-      </c>
-      <c r="V34" s="2">
-        <v>0</v>
-      </c>
-      <c r="W34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="X34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y34" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="2">
+      <c r="P34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R34" s="7">
+        <v>1</v>
+      </c>
+      <c r="S34" s="7">
+        <v>0</v>
+      </c>
+      <c r="T34" s="7">
+        <v>0</v>
+      </c>
+      <c r="U34" s="7">
+        <v>0</v>
+      </c>
+      <c r="V34" s="7">
+        <v>0</v>
+      </c>
+      <c r="W34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="X34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="7">
         <v>50</v>
       </c>
-      <c r="AA34" s="2">
+      <c r="AA34" s="7">
         <v>50</v>
       </c>
-      <c r="AB34" s="3">
-        <v>2876</v>
-      </c>
-      <c r="AC34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AE34" s="3">
+      <c r="AB34" s="6">
+        <v>2576</v>
+      </c>
+      <c r="AC34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="7">
+        <v>-1</v>
+      </c>
+      <c r="AE34" s="6">
         <v>12</v>
       </c>
-      <c r="AF34" s="3">
+      <c r="AF34" s="6">
         <v>12</v>
       </c>
-      <c r="AG34" s="3">
+      <c r="AG34" s="6">
         <v>12</v>
       </c>
-      <c r="AH34" s="3">
+      <c r="AH34" s="6">
         <v>12</v>
       </c>
-      <c r="AI34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="3">
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
         <v>1600000</v>
       </c>
-      <c r="AK34" s="3">
-        <v>1</v>
-      </c>
-      <c r="AL34" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM34" s="2">
+      <c r="AK34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM34" s="7">
         <v>32000</v>
       </c>
-      <c r="AN34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY34" s="2" t="str">
+      <c r="AN34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AR34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AS34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AT34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AU34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AV34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AW34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AX34" s="7">
+        <v>0</v>
+      </c>
+      <c r="AY34" s="7" t="str">
         <f t="shared" si="0"/>
         <v>tunlo032</v>
       </c>
-      <c r="AZ34" s="3">
-        <v>-1</v>
-      </c>
-      <c r="BA34" s="3">
-        <v>2</v>
-      </c>
-      <c r="BB34" s="2"/>
+      <c r="AZ34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BA34" s="6">
+        <v>2</v>
+      </c>
+      <c r="BB34" s="7"/>
     </row>
     <row r="35" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
@@ -20727,7 +20744,7 @@
       </c>
       <c r="AB34">
         <f>UnitLower!AB34</f>
-        <v>2876</v>
+        <v>2576</v>
       </c>
       <c r="AC34">
         <f>UnitLower!AE34</f>

--- a/gu_in/Item.edf/39_UnitLower/UnitLower.xlsx
+++ b/gu_in/Item.edf/39_UnitLower/UnitLower.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5285DFC6-E9C1-4533-A0EB-5EF904592C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F648E2-66C0-41BE-BC9E-A9CE28F00916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="6">
-        <v>1600000</v>
+        <v>90909382</v>
       </c>
       <c r="AK34" s="6">
         <v>1</v>
@@ -20682,7 +20682,7 @@
       </c>
       <c r="I34">
         <f>UnitLower!AJ34</f>
-        <v>1600000</v>
+        <v>90909382</v>
       </c>
       <c r="J34">
         <f>UnitLower!AK34</f>

--- a/gu_in/Item.edf/39_UnitLower/UnitLower.xlsx
+++ b/gu_in/Item.edf/39_UnitLower/UnitLower.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F648E2-66C0-41BE-BC9E-A9CE28F00916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9077581B-4EE2-4DB6-AC53-61E5D1FA986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitLower" sheetId="1" r:id="rId1"/>
@@ -844,7 +844,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -869,6 +869,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -907,7 +913,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -917,6 +923,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -937,9 +946,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -977,9 +986,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1012,26 +1021,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1064,26 +1056,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3430,168 +3405,168 @@
       </c>
       <c r="BB13" s="2"/>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:54" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="3">
-        <v>2</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C14" s="9">
+        <v>2</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="E14" s="3">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="9">
+        <v>2</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="H14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="I14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J14" s="2">
-        <v>0</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="G14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="10">
+        <v>0</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
         <v>45</v>
       </c>
-      <c r="M14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="N14" s="3">
-        <v>2</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="M14" s="9">
+        <v>-1</v>
+      </c>
+      <c r="N14" s="9">
+        <v>2</v>
+      </c>
+      <c r="O14" s="9">
         <v>78</v>
       </c>
-      <c r="P14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="R14" s="2">
-        <v>1</v>
-      </c>
-      <c r="S14" s="2">
-        <v>0</v>
-      </c>
-      <c r="T14" s="2">
-        <v>0</v>
-      </c>
-      <c r="U14" s="2">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2">
-        <v>0</v>
-      </c>
-      <c r="W14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="X14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="2">
+      <c r="P14" s="9">
+        <v>-1</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R14" s="10">
+        <v>1</v>
+      </c>
+      <c r="S14" s="10">
+        <v>0</v>
+      </c>
+      <c r="T14" s="10">
+        <v>0</v>
+      </c>
+      <c r="U14" s="10">
+        <v>0</v>
+      </c>
+      <c r="V14" s="10">
+        <v>0</v>
+      </c>
+      <c r="W14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="X14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="Y14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="10">
         <v>50</v>
       </c>
-      <c r="AA14" s="2">
+      <c r="AA14" s="10">
         <v>50</v>
       </c>
-      <c r="AB14" s="3">
-        <v>5800</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AB14" s="9">
+        <v>5400</v>
+      </c>
+      <c r="AC14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="10">
+        <v>-1</v>
+      </c>
+      <c r="AE14" s="9">
         <v>20</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="9">
         <v>20</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="9">
         <v>20</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="9">
         <v>20</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="3">
-        <v>1600000</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>1</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>1</v>
-      </c>
-      <c r="AM14" s="2">
-        <v>32000</v>
-      </c>
-      <c r="AN14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX14" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY14" s="2" t="str">
+      <c r="AI14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="6">
+        <v>3300000</v>
+      </c>
+      <c r="AK14" s="9">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="9">
+        <v>1</v>
+      </c>
+      <c r="AM14" s="6">
+        <v>330000</v>
+      </c>
+      <c r="AN14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AX14" s="10">
+        <v>0</v>
+      </c>
+      <c r="AY14" s="10" t="str">
         <f t="shared" si="0"/>
         <v>tunlo012</v>
       </c>
-      <c r="AZ14" s="3">
-        <v>-1</v>
-      </c>
-      <c r="BA14" s="3">
-        <v>2</v>
-      </c>
-      <c r="BB14" s="2"/>
+      <c r="AZ14" s="9">
+        <v>-1</v>
+      </c>
+      <c r="BA14" s="9">
+        <v>2</v>
+      </c>
+      <c r="BB14" s="10"/>
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
@@ -6797,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="6">
-        <v>90909382</v>
+        <v>3300000</v>
       </c>
       <c r="AK34" s="6">
         <v>1</v>
@@ -6805,8 +6780,8 @@
       <c r="AL34" s="6">
         <v>1</v>
       </c>
-      <c r="AM34" s="7">
-        <v>32000</v>
+      <c r="AM34" s="6">
+        <v>330000</v>
       </c>
       <c r="AN34" s="7">
         <v>0</v>
@@ -17082,7 +17057,7 @@
       </c>
       <c r="I14">
         <f>UnitLower!AJ14</f>
-        <v>1600000</v>
+        <v>3300000</v>
       </c>
       <c r="J14">
         <f>UnitLower!AK14</f>
@@ -17144,7 +17119,7 @@
       </c>
       <c r="AB14">
         <f>UnitLower!AB14</f>
-        <v>5800</v>
+        <v>5400</v>
       </c>
       <c r="AC14">
         <f>UnitLower!AE14</f>
@@ -20682,7 +20657,7 @@
       </c>
       <c r="I34">
         <f>UnitLower!AJ34</f>
-        <v>90909382</v>
+        <v>3300000</v>
       </c>
       <c r="J34">
         <f>UnitLower!AK34</f>

--- a/gu_in/Item.edf/39_UnitLower/UnitLower.xlsx
+++ b/gu_in/Item.edf/39_UnitLower/UnitLower.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9077581B-4EE2-4DB6-AC53-61E5D1FA986F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4FF2E6-6DC5-4EF1-A5BF-D803AE3AEF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UnitLower" sheetId="1" r:id="rId1"/>
@@ -946,9 +946,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -986,9 +986,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1021,9 +1021,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1056,9 +1073,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6772,7 +6806,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" s="6">
-        <v>3300000</v>
+        <v>6600000</v>
       </c>
       <c r="AK34" s="6">
         <v>1</v>
@@ -6781,7 +6815,7 @@
         <v>1</v>
       </c>
       <c r="AM34" s="6">
-        <v>330000</v>
+        <v>909091</v>
       </c>
       <c r="AN34" s="7">
         <v>0</v>
@@ -20657,7 +20691,7 @@
       </c>
       <c r="I34">
         <f>UnitLower!AJ34</f>
-        <v>3300000</v>
+        <v>6600000</v>
       </c>
       <c r="J34">
         <f>UnitLower!AK34</f>
